--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,100 @@
       </c>
       <c r="K4" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>belt_t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>logistics.tier.t2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>build.tool.belt_t2.desc</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>belt_t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>logistics.tier.t3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>build.tool.belt_t3.desc</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>belt=传送带(按住拖拽铺设)</t>
+          <t>belt=传送带(按住拖拽铺设);splitter=分流器;merger=合流器(单击放置);underground=地下传送带(从入口拖到出口)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>传送带等级:0=T1,1=T2,2=T3</t>
+          <t>传送带等级:0=T1,1=T2,2=T3(分流器/合流器=内部速度档)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -726,6 +726,241 @@
       </c>
       <c r="K6" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>splitter</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>splitter</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>logistics.node.splitter</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>build.tool.splitter.desc</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>merger</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>merger</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>logistics.node.merger</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>build.tool.merger.desc</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>underground_t1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>underground</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>logistics.underground.t1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>build.tool.underground_t1.desc</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>underground_t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>underground</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>logistics.underground.t2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>build.tool.underground_t2.desc</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>underground_t3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>underground</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>logistics.underground.t3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>build.tool.underground_t3.desc</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>belt=传送带(按住拖拽铺设);splitter=分流器;merger=合流器(单击放置);underground=地下传送带(从入口拖到出口)</t>
+          <t>belt=传送带(按住拖拽铺设);splitter=分流器;merger=合流器(单击放置);underground=地下传送带(从入口拖到出口);pipe=管线(拖拽);pump=泵/tank=储罐/valve=阀门(单击放置)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>传送带等级:0=T1,1=T2,2=T3(分流器/合流器=内部速度档)</t>
+          <t>传送带等级:0=T1,1=T2,2=T3(分流器/合流器=内部速度档);管线0=T1,1=T2;泵/储罐/阀门填0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -961,6 +961,241 @@
       </c>
       <c r="K11" t="n">
         <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pipe_t1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>logistics.pipe.t1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>build.tool.pipe_t1.desc</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pipe_t2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>logistics.pipe.t2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>build.tool.pipe_t2.desc</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>logistics.pipe.pump</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>build.tool.pump.desc</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>logistics.pipe.tank</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>build.tool.tank.desc</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>logistics.pipe.valve</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>build.tool.valve.desc</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,6 +1198,100 @@
         <v>44</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pipe_underground_t1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pipe_underground</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>logistics.pipe.underground_t1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>build.tool.pipe_underground_t1.desc</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pipe_underground_t2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pipe_underground</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>logistics.pipe.underground_t2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>build.tool.pipe_underground_t2.desc</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -669,12 +669,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.belt_t2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.belt_t2</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -716,12 +716,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.belt_t3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.belt_t3</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.splitter</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.splitter</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -810,12 +810,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.splitter</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.splitter</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -857,12 +857,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.underground</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.underground</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -904,12 +904,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.belt_t2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.belt_t2</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -951,12 +951,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.belt_t3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.belt_t3</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.pipe_t2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.pipe_t2</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.pipe_underground</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.pipe_underground</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.pipe_t2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.pipe_t2</t>
         </is>
       </c>
       <c r="K18" t="n">

--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,6 +1292,100 @@
         <v>46</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pipe_t3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>logistics.pipe.t3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>build.tool.pipe_t3.desc</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>research:logistics.heat_trace</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>research.hint.logistics.heat_trace</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>roof</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>roof</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>env.roof.name</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>build.tool.roof.desc</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>research:environment.roof</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>research.hint.environment.roof</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildTool-建造菜单工具.xlsx
@@ -622,12 +622,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>pace:belts_open</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>pace.hint.belts_open</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -669,7 +669,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>research:logistics.belt_t2</t>
+          <t>research:logistics.belt_t2&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>research:logistics.belt_t3</t>
+          <t>research:logistics.belt_t3&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>research:logistics.splitter</t>
+          <t>research:logistics.splitter&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>research:logistics.splitter</t>
+          <t>research:logistics.splitter&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>research:logistics.underground</t>
+          <t>research:logistics.underground&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>research:logistics.belt_t2</t>
+          <t>research:logistics.belt_t2&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>research:logistics.belt_t3</t>
+          <t>research:logistics.belt_t3&amp;pace:belts_open</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
